--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.95563428627354</v>
+        <v>2.105290571519451</v>
       </c>
       <c r="D2" t="n">
-        <v>12.80742619716864</v>
+        <v>2.081206757039904</v>
       </c>
       <c r="E2" t="n">
-        <v>6.805024185642515</v>
+        <v>1.105816430166909</v>
       </c>
       <c r="F2" t="n">
-        <v>9.1707050285882</v>
+        <v>1.490239567145582</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.56568265755857</v>
+        <v>4.316923431853268</v>
       </c>
       <c r="D3" t="n">
-        <v>31.14883625434504</v>
+        <v>5.061685891331069</v>
       </c>
       <c r="E3" t="n">
-        <v>6.805024185642515</v>
+        <v>1.105816430166909</v>
       </c>
       <c r="F3" t="n">
-        <v>9.1707050285882</v>
+        <v>1.490239567145582</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
